--- a/NF_factor.xlsx
+++ b/NF_factor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEBD858-6FE0-4CD3-AA71-B7B22AB89C52}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D84199-3058-466D-A311-08A2A42A9DDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" activeTab="6" xr2:uid="{D1DA9D51-73AD-475A-9BA4-9259CC4D49A6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" firstSheet="1" activeTab="6" xr2:uid="{D1DA9D51-73AD-475A-9BA4-9259CC4D49A6}"/>
   </bookViews>
   <sheets>
     <sheet name="midpoint" sheetId="1" r:id="rId1"/>
@@ -470,6 +470,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4546,157 +4547,177 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="Waste_characteristics"/>
       <sheetName val="LCI"/>
+      <sheetName val="SP_mid"/>
+      <sheetName val="SP_end"/>
       <sheetName val="Parameters"/>
-      <sheetName val="Waste_characteristics"/>
+      <sheetName val="Feuil5"/>
+      <sheetName val="HC_end"/>
+      <sheetName val="HC_mid"/>
+      <sheetName val="IC_mid"/>
+      <sheetName val="IC_end"/>
+      <sheetName val="impact_process_end"/>
+      <sheetName val="impact_process_mid"/>
       <sheetName val="AD_a_end"/>
       <sheetName val="AD_a_mid"/>
-      <sheetName val="impact_process_mid"/>
-      <sheetName val="impact_process_end"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="21">
-          <cell r="C21">
-            <v>1.2563005899482752E-8</v>
-          </cell>
-          <cell r="D21">
-            <v>7.508434002465424E-12</v>
-          </cell>
-          <cell r="E21">
-            <v>2.7491055024070358E-7</v>
-          </cell>
-          <cell r="F21">
-            <v>3.2127854164427263E-10</v>
-          </cell>
-          <cell r="G21">
-            <v>6.3601576075550474E-11</v>
-          </cell>
-          <cell r="H21">
-            <v>5.7922708436740248E-10</v>
-          </cell>
-          <cell r="I21">
-            <v>1.2031466728762197E-9</v>
-          </cell>
-          <cell r="J21">
-            <v>1.1349905410927971E-12</v>
-          </cell>
-          <cell r="K21">
-            <v>2.8013169449408218E-8</v>
-          </cell>
-          <cell r="L21">
-            <v>1.9849153382948159E-8</v>
-          </cell>
-          <cell r="M21">
-            <v>1.1865594419752642E-13</v>
-          </cell>
-          <cell r="N21">
-            <v>2.6520782229579583E-9</v>
-          </cell>
-          <cell r="O21">
-            <v>9.1280201075265318E-5</v>
-          </cell>
-          <cell r="P21">
-            <v>2.1815781008080298E-6</v>
-          </cell>
-          <cell r="Q21">
-            <v>2.7108573172813371E-6</v>
-          </cell>
-          <cell r="R21">
-            <v>2.2622869023682998E-7</v>
-          </cell>
-          <cell r="S21">
-            <v>1.0803650962912509E-7</v>
-          </cell>
-          <cell r="T21">
-            <v>2.2764499221779344E-5</v>
-          </cell>
-          <cell r="U21">
-            <v>1.1115681494988516E-7</v>
-          </cell>
-          <cell r="V21">
-            <v>4.3611952999753085E-7</v>
-          </cell>
-          <cell r="W21">
-            <v>1.8062472922938586</v>
-          </cell>
-          <cell r="X21">
-            <v>4.2251223605615285E-2</v>
-          </cell>
-          <cell r="Y21">
-            <v>3.3751164211148037E-7</v>
-          </cell>
-          <cell r="Z21">
-            <v>1.1981857215673038E-4</v>
-          </cell>
-          <cell r="AA21">
-            <v>1.848498518551553</v>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="24">
+          <cell r="E24">
+            <v>2161.4235062008215</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4">
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12">
         <row r="21">
           <cell r="C21">
-            <v>5.9240090526703038E-2</v>
+            <v>2.0114159106083146E-8</v>
           </cell>
           <cell r="D21">
-            <v>98.180762487623426</v>
+            <v>8.6310788099342979E-12</v>
           </cell>
           <cell r="E21">
-            <v>0.46426196825745414</v>
+            <v>3.1600059197708628E-7</v>
           </cell>
           <cell r="F21">
-            <v>0.60496125978395132</v>
+            <v>1.3081537319805549E-9</v>
           </cell>
           <cell r="G21">
-            <v>50.752035262762597</v>
+            <v>2.6432711210404287E-10</v>
           </cell>
           <cell r="H21">
-            <v>5.3113649866823636</v>
+            <v>6.6160130800630221E-10</v>
           </cell>
           <cell r="I21">
-            <v>1.7964144750168079E-3</v>
+            <v>8.3772645802817259E-9</v>
           </cell>
           <cell r="J21">
-            <v>6.6788692112393063E-4</v>
+            <v>5.5049396322898631E-12</v>
           </cell>
           <cell r="K21">
-            <v>0.65722134364281071</v>
+            <v>2.3071054374591618E-8</v>
           </cell>
           <cell r="L21">
-            <v>11.892521138124106</v>
+            <v>3.0363862070667683E-8</v>
           </cell>
           <cell r="M21">
-            <v>26.667638722324341</v>
+            <v>3.3537816916510031E-13</v>
           </cell>
           <cell r="N21">
-            <v>3.1591540366112709</v>
+            <v>7.4960352379616801E-9</v>
           </cell>
           <cell r="O21">
-            <v>0.18265596292469566</v>
+            <v>1.0493603187596104E-4</v>
           </cell>
           <cell r="P21">
-            <v>2.0349428493145704E-4</v>
+            <v>9.6426650123120094E-6</v>
           </cell>
           <cell r="Q21">
-            <v>3.621297316729697E-2</v>
+            <v>1.7843126973875924E-5</v>
           </cell>
           <cell r="R21">
-            <v>0.12208712230514712</v>
+            <v>1.5324405242813227E-7</v>
           </cell>
           <cell r="S21">
-            <v>0.15389147145023696</v>
+            <v>2.0861594309566321E-7</v>
           </cell>
           <cell r="T21">
-            <v>0.19645023873762654</v>
+            <v>2.9355788783269308E-5</v>
+          </cell>
+          <cell r="U21">
+            <v>1.7684554542813573E-7</v>
+          </cell>
+          <cell r="V21">
+            <v>1.2326813502425872E-6</v>
+          </cell>
+          <cell r="W21">
+            <v>1.7934536989911445</v>
+          </cell>
+          <cell r="X21">
+            <v>9.2289169396780252E-2</v>
+          </cell>
+          <cell r="Y21">
+            <v>4.0017516831963653E-7</v>
+          </cell>
+          <cell r="Z21">
+            <v>1.6354887029820838E-4</v>
+          </cell>
+          <cell r="AA21">
+            <v>1.8857428758839609</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="13">
+        <row r="21">
+          <cell r="C21">
+            <v>9.4856034682359522E-2</v>
+          </cell>
+          <cell r="D21">
+            <v>112.85816964360667</v>
+          </cell>
+          <cell r="E21">
+            <v>1.8897909850913781</v>
+          </cell>
+          <cell r="F21">
+            <v>2.5151402305512089</v>
+          </cell>
+          <cell r="G21">
+            <v>57.989682361285929</v>
+          </cell>
+          <cell r="H21">
+            <v>5.3058827775119699</v>
+          </cell>
+          <cell r="I21">
+            <v>1.2508914597501019E-2</v>
+          </cell>
+          <cell r="J21">
+            <v>3.239974608119197E-3</v>
+          </cell>
+          <cell r="K21">
+            <v>2.9052166220844349</v>
+          </cell>
+          <cell r="L21">
+            <v>78.290448949194143</v>
+          </cell>
+          <cell r="M21">
+            <v>18.064265874973131</v>
+          </cell>
+          <cell r="N21">
+            <v>2.6016536342186303</v>
+          </cell>
+          <cell r="O21">
+            <v>0.39896912087880565</v>
+          </cell>
+          <cell r="P21">
+            <v>3.9294180257441866E-4</v>
+          </cell>
+          <cell r="Q21">
+            <v>4.6701004574385654E-2</v>
+          </cell>
+          <cell r="R21">
+            <v>0.19425384155122416</v>
+          </cell>
+          <cell r="S21">
+            <v>0.23540744381477383</v>
+          </cell>
+          <cell r="T21">
+            <v>0.55526186947864298</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5002,7 +5023,7 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="103.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="113.08984375" customWidth="1"/>
     <col min="2" max="2" width="31.54296875" customWidth="1"/>
     <col min="3" max="3" width="21.6328125" customWidth="1"/>
   </cols>
@@ -5235,6 +5256,7 @@
   <cols>
     <col min="1" max="1" width="75.54296875" customWidth="1"/>
     <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -5631,7 +5653,7 @@
       </c>
       <c r="G3" s="17">
         <f>[1]AD_a_mid!$C$21</f>
-        <v>5.9240090526703038E-2</v>
+        <v>9.4856034682359522E-2</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
@@ -5649,7 +5671,7 @@
       </c>
       <c r="G4" s="17">
         <f>[1]AD_a_mid!$D$21</f>
-        <v>98.180762487623426</v>
+        <v>112.85816964360667</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
@@ -5667,7 +5689,7 @@
       </c>
       <c r="G5" s="17">
         <f>[1]AD_a_mid!$E$21</f>
-        <v>0.46426196825745414</v>
+        <v>1.8897909850913781</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
@@ -5685,7 +5707,7 @@
       </c>
       <c r="G6" s="17">
         <f>[1]AD_a_mid!$F$21</f>
-        <v>0.60496125978395132</v>
+        <v>2.5151402305512089</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
@@ -5703,7 +5725,7 @@
       </c>
       <c r="G7" s="17">
         <f>[1]AD_a_mid!$G$21</f>
-        <v>50.752035262762597</v>
+        <v>57.989682361285929</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
@@ -5721,7 +5743,7 @@
       </c>
       <c r="G8" s="17">
         <f>[1]AD_a_mid!$H$21</f>
-        <v>5.3113649866823636</v>
+        <v>5.3058827775119699</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
@@ -5739,7 +5761,7 @@
       </c>
       <c r="G9" s="17">
         <f>[1]AD_a_mid!$I$21</f>
-        <v>1.7964144750168079E-3</v>
+        <v>1.2508914597501019E-2</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
@@ -5757,7 +5779,7 @@
       </c>
       <c r="G10" s="17">
         <f>[1]AD_a_mid!$J$21</f>
-        <v>6.6788692112393063E-4</v>
+        <v>3.239974608119197E-3</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
@@ -5775,7 +5797,7 @@
       </c>
       <c r="G11" s="17">
         <f>[1]AD_a_mid!$K$21</f>
-        <v>0.65722134364281071</v>
+        <v>2.9052166220844349</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
@@ -5793,7 +5815,7 @@
       </c>
       <c r="G12" s="17">
         <f>[1]AD_a_mid!$L$21</f>
-        <v>11.892521138124106</v>
+        <v>78.290448949194143</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
@@ -5811,7 +5833,7 @@
       </c>
       <c r="G13" s="17">
         <f>[1]AD_a_mid!$M$21</f>
-        <v>26.667638722324341</v>
+        <v>18.064265874973131</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -5829,7 +5851,7 @@
       </c>
       <c r="G14" s="17">
         <f>[1]AD_a_mid!$N$21</f>
-        <v>3.1591540366112709</v>
+        <v>2.6016536342186303</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
@@ -5847,7 +5869,7 @@
       </c>
       <c r="G15" s="17">
         <f>[1]AD_a_mid!$O$21</f>
-        <v>0.18265596292469566</v>
+        <v>0.39896912087880565</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
@@ -5865,7 +5887,7 @@
       </c>
       <c r="G16" s="17">
         <f>[1]AD_a_mid!$P$21</f>
-        <v>2.0349428493145704E-4</v>
+        <v>3.9294180257441866E-4</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -5883,7 +5905,7 @@
       </c>
       <c r="G17" s="17">
         <f>[1]AD_a_mid!$Q$21</f>
-        <v>3.621297316729697E-2</v>
+        <v>4.6701004574385654E-2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -5901,7 +5923,7 @@
       </c>
       <c r="G18" s="17">
         <f>[1]AD_a_mid!$R$21</f>
-        <v>0.12208712230514712</v>
+        <v>0.19425384155122416</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -5919,7 +5941,7 @@
       </c>
       <c r="G19" s="17">
         <f>[1]AD_a_mid!$S$21</f>
-        <v>0.15389147145023696</v>
+        <v>0.23540744381477383</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -5937,7 +5959,7 @@
       </c>
       <c r="G20">
         <f>[1]AD_a_mid!$T$21</f>
-        <v>0.19645023873762654</v>
+        <v>0.55526186947864298</v>
       </c>
     </row>
   </sheetData>
@@ -5952,6 +5974,8 @@
   <cols>
     <col min="1" max="1" width="65.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.54296875" customWidth="1"/>
+    <col min="9" max="9" width="23.08984375" customWidth="1"/>
+    <col min="15" max="15" width="19.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
@@ -6022,7 +6046,7 @@
       </c>
       <c r="G2" s="4">
         <f>[1]AD_a_end!$C$21</f>
-        <v>1.2563005899482752E-8</v>
+        <v>2.0114159106083146E-8</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
@@ -6034,7 +6058,7 @@
       </c>
       <c r="G3" s="4">
         <f>[1]AD_a_end!$D$21</f>
-        <v>7.508434002465424E-12</v>
+        <v>8.6310788099342979E-12</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
@@ -6046,7 +6070,7 @@
       </c>
       <c r="G4" s="4">
         <f>[1]AD_a_end!$E$21</f>
-        <v>2.7491055024070358E-7</v>
+        <v>3.1600059197708628E-7</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
@@ -6058,7 +6082,7 @@
       </c>
       <c r="G5" s="4">
         <f>[1]AD_a_end!$F$21</f>
-        <v>3.2127854164427263E-10</v>
+        <v>1.3081537319805549E-9</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
@@ -6070,7 +6094,7 @@
       </c>
       <c r="G6" s="4">
         <f>[1]AD_a_end!$G$21</f>
-        <v>6.3601576075550474E-11</v>
+        <v>2.6432711210404287E-10</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
@@ -6082,7 +6106,7 @@
       </c>
       <c r="G7" s="4">
         <f>[1]AD_a_end!$H$21</f>
-        <v>5.7922708436740248E-10</v>
+        <v>6.6160130800630221E-10</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
@@ -6094,7 +6118,7 @@
       </c>
       <c r="G8" s="4">
         <f>[1]AD_a_end!$I$21</f>
-        <v>1.2031466728762197E-9</v>
+        <v>8.3772645802817259E-9</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
@@ -6106,7 +6130,7 @@
       </c>
       <c r="G9" s="4">
         <f>[1]AD_a_end!$J$21</f>
-        <v>1.1349905410927971E-12</v>
+        <v>5.5049396322898631E-12</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
@@ -6118,7 +6142,7 @@
       </c>
       <c r="G10" s="4">
         <f>[1]AD_a_end!$K$21</f>
-        <v>2.8013169449408218E-8</v>
+        <v>2.3071054374591618E-8</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
@@ -6130,7 +6154,7 @@
       </c>
       <c r="G11" s="4">
         <f>[1]AD_a_end!$L$21</f>
-        <v>1.9849153382948159E-8</v>
+        <v>3.0363862070667683E-8</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
@@ -6142,7 +6166,7 @@
       </c>
       <c r="G12" s="4">
         <f>[1]AD_a_end!$M$21</f>
-        <v>1.1865594419752642E-13</v>
+        <v>3.3537816916510031E-13</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
@@ -6154,7 +6178,7 @@
       </c>
       <c r="G13" s="4">
         <f>[1]AD_a_end!$N$21</f>
-        <v>2.6520782229579583E-9</v>
+        <v>7.4960352379616801E-9</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -6166,7 +6190,7 @@
       </c>
       <c r="G14" s="4">
         <f>[1]AD_a_end!$O$21</f>
-        <v>9.1280201075265318E-5</v>
+        <v>1.0493603187596104E-4</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
@@ -6178,7 +6202,7 @@
       </c>
       <c r="G15" s="4">
         <f>[1]AD_a_end!$P$21</f>
-        <v>2.1815781008080298E-6</v>
+        <v>9.6426650123120094E-6</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
@@ -6190,7 +6214,7 @@
       </c>
       <c r="G16" s="4">
         <f>[1]AD_a_end!$Q$21</f>
-        <v>2.7108573172813371E-6</v>
+        <v>1.7843126973875924E-5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -6202,7 +6226,7 @@
       </c>
       <c r="G17" s="4">
         <f>[1]AD_a_end!$R$21</f>
-        <v>2.2622869023682998E-7</v>
+        <v>1.5324405242813227E-7</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -6214,7 +6238,7 @@
       </c>
       <c r="G18" s="4">
         <f>[1]AD_a_end!$S$21</f>
-        <v>1.0803650962912509E-7</v>
+        <v>2.0861594309566321E-7</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -6226,7 +6250,7 @@
       </c>
       <c r="G19" s="4">
         <f>[1]AD_a_end!$T$21</f>
-        <v>2.2764499221779344E-5</v>
+        <v>2.9355788783269308E-5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -6238,7 +6262,7 @@
       </c>
       <c r="G20" s="4">
         <f>[1]AD_a_end!$U$21</f>
-        <v>1.1115681494988516E-7</v>
+        <v>1.7684554542813573E-7</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -6250,7 +6274,7 @@
       </c>
       <c r="G21" s="4">
         <f>[1]AD_a_end!$V$21</f>
-        <v>4.3611952999753085E-7</v>
+        <v>1.2326813502425872E-6</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -6262,7 +6286,7 @@
       </c>
       <c r="G22" s="4">
         <f>[1]AD_a_end!$W$21</f>
-        <v>1.8062472922938586</v>
+        <v>1.7934536989911445</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -6274,7 +6298,7 @@
       </c>
       <c r="G23" s="4">
         <f>[1]AD_a_end!$X$21</f>
-        <v>4.2251223605615285E-2</v>
+        <v>9.2289169396780252E-2</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -6286,7 +6310,7 @@
       </c>
       <c r="G24" s="4">
         <f>[1]AD_a_end!$Y$21</f>
-        <v>3.3751164211148037E-7</v>
+        <v>4.0017516831963653E-7</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -6298,7 +6322,7 @@
       </c>
       <c r="G25" s="4">
         <f>[1]AD_a_end!$Z$21</f>
-        <v>1.1981857215673038E-4</v>
+        <v>1.6354887029820838E-4</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -6307,7 +6331,7 @@
       </c>
       <c r="G26" s="4">
         <f>[1]AD_a_end!$AA$21</f>
-        <v>1.848498518551553</v>
+        <v>1.8857428758839609</v>
       </c>
     </row>
   </sheetData>
@@ -6321,6 +6345,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="106.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.36328125" customWidth="1"/>
     <col min="3" max="3" width="27.453125" customWidth="1"/>
     <col min="4" max="4" width="26.453125" customWidth="1"/>
     <col min="6" max="6" width="16.54296875" customWidth="1"/>
